--- a/StructureDefinition-inera-ehds-observation-base.xlsx
+++ b/StructureDefinition-inera-ehds-observation-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T07:52:35+00:00</t>
+    <t>2026-09-30T09:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1003,7 +1003,7 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding {http://hl7.org/fhir/uv/ips/StructureDefinition/Coding-uv-ips}
+    <t xml:space="preserve">Coding {http://hl7.org/fhir/uv/ips/StructureDefinition/Coding-uv-ips|2.0.1}
 </t>
   </si>
   <si>
@@ -1076,7 +1076,7 @@
     <t>translation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {translation|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {translation|5.3.0}
 </t>
   </si>
   <si>

--- a/StructureDefinition-inera-ehds-observation-base.xlsx
+++ b/StructureDefinition-inera-ehds-observation-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:02:48+00:00</t>
+    <t>2026-09-30T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-observation-base.xlsx
+++ b/StructureDefinition-inera-ehds-observation-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:52:57+00:00</t>
+    <t>2026-10-01T18:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-observation-base.xlsx
+++ b/StructureDefinition-inera-ehds-observation-base.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T18:35:17+00:00</t>
+    <t>2026-10-02T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -451,7 +451,7 @@
 </t>
   </si>
   <si>
-    <t>Källsystem (header) – HSA-id för det system som tillgängliggör informationen</t>
+    <t>Källsystem (header) – HSA-id för det system som tillgängliggör informationen – https://tjanstekatalogen.inera.se/Endpoint/{hsaId} (GENERAL-005)</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
@@ -1003,7 +1003,7 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding {http://hl7.org/fhir/uv/ips/StructureDefinition/Coding-uv-ips|2.0.1}
+    <t xml:space="preserve">Coding {http://hl7.org/fhir/uv/ips/StructureDefinition/Coding-uv-ips}
 </t>
   </si>
   <si>
@@ -1076,7 +1076,7 @@
     <t>translation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {translation|5.3.0}
+    <t xml:space="preserve">Extension {translation|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
